--- a/daily_matches/job_matches_2026-05-27.xlsx
+++ b/daily_matches/job_matches_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, XGBoost</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3462d2e2223e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Springwood Backend Developer (Hybrid)</t>
+          <t>Senior Analytics Engineer, People Data</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12483420b6facc39</t>
+          <t>https://www.indeed.com/viewjob?jk=d5886aefde3a2ed5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer, People Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A-TEK Inc</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Synapse, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Databricks, PySpark, Kafka</t>
+          <t>RAG, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdcddba2d97d56f1</t>
+          <t>https://www.indeed.com/viewjob?jk=392458a76ed6493b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Prompt Engineer</t>
+          <t>Forward Deployed Engineer - Data Migration &amp; Data Consolidation Platforms</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Rackspace Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker</t>
+          <t>RAG, Glue, Redshift, BigQuery, Synapse, Kinesis, CI/CD, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d32a2eabd210ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=b3063b040bfb390f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Architect/Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, XGBoost, Docker, CI/CD, Terraform, PostgreSQL, NoSQL</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, AWS SageMaker, S3, Glue, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc83cb585d053a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infrastructure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Moloco</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, CI/CD, Git</t>
+          <t>RAG, Mistral, Pinecone, Prompt Engineering, S3, FastAPI, CI/CD, Git, PostgreSQL, Matplotlib</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8ef143aa3b8032</t>
+          <t>https://www.indeed.com/viewjob?jk=f8cd3096eac30881</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Growth</t>
+          <t>ML Ops Technical Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, EC2, Terraform, Git, MySQL, Cassandra, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, BigQuery, Git, BigQuery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f116fb4b6f0698</t>
+          <t>https://www.indeed.com/viewjob?jk=ba032ff3415ade07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Infrastructure Engineer-Full Time (US /LATAM)</t>
+          <t>Devops Engineer- Dallas, TX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Very Good Ventures</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e88263ff5eac8d</t>
+          <t>https://www.indeed.com/viewjob?jk=b54ee210402c3773</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer II - Surgery</t>
+          <t>Senior Data Scientist, AI Foundations</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, PostgreSQL, MySQL, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, PyTorch, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443f2bd8cdbdcd91</t>
+          <t>https://www.indeed.com/viewjob?jk=fdbb9fc911d813dc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Environmental Resources Management</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, S3, FastAPI, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e934ffe2db88658f</t>
+          <t>https://www.indeed.com/viewjob?jk=78902f746ba9d9e9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Architect – Manufacturing Test</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, Python, R, Java</t>
+          <t>Generative AI, RAG, CI/CD, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41f58d52e9bbbef</t>
+          <t>https://www.indeed.com/viewjob?jk=1c04a9f371533f2c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Translational Genomics</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Broad Institute</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a96dfa4a61b04e92</t>
+          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI (Artificial Intelligence) QA Software Engineer</t>
+          <t>Software Architect – Manufacturing Test</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5a4bd8a291d9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=132ec3a8e9018054</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Partnerships Solutions Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, LLaMA, Mistral, Prompt Engineering, GCP Vertex AI, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864392f64d0290f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e679e79ba540faf8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Security Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, Git, PostgreSQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ededa18e13eb68</t>
+          <t>https://www.indeed.com/viewjob?jk=c554064daacf6b24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer - AI/ML for Hyperspectral Imaging</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lawrence Berkeley National Laboratory</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, MLflow, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=546d0f30bf1c2889</t>
+          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Workflow Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, AKS, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Mistral, Docker, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03caa9b0c403647b</t>
+          <t>https://www.indeed.com/viewjob?jk=e560c4f5d9bc08ad</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI / Machine Learning Engineer</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Scala</t>
+          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,42 +1091,637 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3541a7549c4dc4a</t>
+          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer – Entry Level</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Niwot, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46dcb4c5b0048b8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2581a16deea24f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Township of Hamilton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>S3, EC2, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09ecad913ea95b78</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Associate AI Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cornerstone OnDemand</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dublin, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e216bb96277572f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Specialized Dental</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Franklin, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Copilot, Apache Airflow, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97619fb277569f5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Product Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, S3, MLflow, Docker, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6799746f191c8419</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - Pre Training</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Mindbeam</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1e9f354640d780e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Marketing</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Scopely</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=556df3a77af59691</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Scientist – Business Intelligence (Decision Science Focus)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Keysight Technologies</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Synapse, Snowflake, Databricks, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5e05d3d0fc8aa98</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist/Data Analytics – R01565538</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Brillio LLC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Keras, PySpark, Power BI, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=deb9d13f0cc9eea7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, S3, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f38cfa20e55b339</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Kafka, Cassandra, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3887d74faedf394</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Generalist</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Arlo Technologies</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, FastAPI, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb5c5b4ad1fbf2e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, AKS, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d00076775d07a5f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Internal Systems Engineer (Applied AI)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Impact.Com</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Santa Barbara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3f1016f224e6b37</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Internal Systems Engineer (Applied AI)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Impact.Com</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=225a243358c68f49</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Automation Test Architect - Agentic AI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Wolters Kluwer</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Coppell, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50866ef8a2d7d819</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Decision Scientist III</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Tableau, Power BI, MicroStrategy, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f925fb9d6621279</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-27.xlsx
+++ b/daily_matches/job_matches_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, People Data</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5886aefde3a2ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, People Data</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,164 +566,164 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=392458a76ed6493b</t>
+          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - Data Migration &amp; Data Consolidation Platforms</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rackspace Technology</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, BigQuery, Synapse, Kinesis, CI/CD, Jenkins, Terraform, Git</t>
+          <t>Generative AI, RAG, Gemini, S3, EC2, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3063b040bfb390f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4df4e36af097a7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, AWS SageMaker, S3, Glue, Docker, Kubernetes</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Databricks, Redshift, PySpark, Hadoop, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
+          <t>https://www.indeed.com/viewjob?jk=87f70fa8d4be0571</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Mistral, Pinecone, Prompt Engineering, S3, FastAPI, CI/CD, Git, PostgreSQL, Matplotlib</t>
+          <t>Data Scientist, Generative AI, LangChain, TensorFlow, PyTorch, XGBoost, Glue, PySpark, Tableau, Matplotlib</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cd3096eac30881</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1ab8ff9cf591e7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ML Ops Technical Architect</t>
+          <t>Senior Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Specialty Building Products</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, BigQuery, Git, BigQuery</t>
+          <t>RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba032ff3415ade07</t>
+          <t>https://www.indeed.com/viewjob?jk=6435e356286a621f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Devops Engineer- Dallas, TX</t>
+          <t>Distinguished Engineer, AI Applications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,274 +731,274 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, Python</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Kubernetes, CI/CD, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b54ee210402c3773</t>
+          <t>https://www.indeed.com/viewjob?jk=ad2682317f293117</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Foundations</t>
+          <t>Distinguished Engineer, AI Applications</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, PyTorch, Git, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Kubernetes, CI/CD, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdbb9fc911d813dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b23e7662e6387489</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Distinguished Engineer, AI Applications</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, FastAPI, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Kubernetes, CI/CD, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78902f746ba9d9e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d62b0b0da2ee68ce</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c04a9f371533f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
+          <t>https://www.indeed.com/viewjob?jk=e71383b94e86fbaa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, PyTorch, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ec3a8e9018054</t>
+          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Partnerships Solutions Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Holtzbrinck Publishing Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Mistral, Prompt Engineering, GCP Vertex AI, Git, Databricks, Python, R</t>
+          <t>AI Engineer, RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, Snowflake, BigQuery, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e679e79ba540faf8</t>
+          <t>https://www.indeed.com/viewjob?jk=6553fe8d88b5cc2c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Security Software Engineer</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, Git, PostgreSQL, MongoDB, Python, SQL, R</t>
+          <t>BigQuery, Kubernetes, CI/CD, Jenkins, Terraform, Git, Snowflake, BigQuery, MySQL, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c554064daacf6b24</t>
+          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,151 +1007,151 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL, R</t>
+          <t>BigQuery, Kubernetes, CI/CD, Jenkins, Terraform, Git, Snowflake, BigQuery, MySQL, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Workflow Architect</t>
+          <t>Senior Software Engineer- Forward Deployed</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Mistral, Docker, Git, NoSQL, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e560c4f5d9bc08ad</t>
+          <t>https://www.indeed.com/viewjob?jk=bda2c2b8bdd5703d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Senior Solutions Architect, GenAI Agentic Networks - Telco</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, PySpark, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Mistral, PyTorch, Docker, Kubernetes, NoSQL, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
+          <t>https://www.indeed.com/viewjob?jk=6910545a799b3e3d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, Glue, Athena, Data Lake, Docker, Terraform, Databricks, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
+          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer – Entry Level</t>
+          <t>AI Enabled Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Customer Value Partners (CVP)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Niwot, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, FastAPI, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46dcb4c5b0048b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b489b3e5c3db2a7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>Cortex, CI/CD, GitHub Actions, Git, Snowflake, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2581a16deea24f9</t>
+          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>AI Engineer – Microsoft Fabric &amp; Azure AI Foundry</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Valtech Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S3, EC2, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Power BI, Python</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,124 +1231,124 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ecad913ea95b78</t>
+          <t>https://www.indeed.com/viewjob?jk=61ca3c21cedbb70b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Associate AI Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Python, R, Java</t>
+          <t>RAG, Glue, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka, SQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e216bb96277572f</t>
+          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Fundamental Equities</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Specialized Dental</t>
+          <t>schonfeld</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Copilot, Apache Airflow, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, EC2, FastAPI, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97619fb277569f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=3273ba88ae98348c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Product Solutions Engineer</t>
+          <t>Backend Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>ClearlyRated</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, S3, MLflow, Docker, CI/CD, Python, SQL, R</t>
+          <t>BigQuery, Dataflow, Kubernetes, CI/CD, Snowflake, BigQuery, Kafka, PostgreSQL, MySQL, SQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6799746f191c8419</t>
+          <t>https://www.indeed.com/viewjob?jk=4fe81f0b261447fa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Pre Training</t>
+          <t>AI Enabled Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mindbeam</t>
+          <t>Customer Value Partners (CVP)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+          <t>RAG, FastAPI, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e9f354640d780e</t>
+          <t>https://www.indeed.com/viewjob?jk=33dfe4ea6a65c4c8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist, Marketing</t>
+          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Scopely</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
+          <t>S3, Glue, Redshift, Kinesis, CI/CD, Terraform, Git, Snowflake, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=556df3a77af59691</t>
+          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist – Business Intelligence (Decision Science Focus)</t>
+          <t>AI Engineer - Advisor Software</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Synapse, Snowflake, Databricks, Power BI, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5e05d3d0fc8aa98</t>
+          <t>https://www.indeed.com/viewjob?jk=4621e3a1c0e29479</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Data Analytics – R01565538</t>
+          <t>MES Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>United States Steel</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Keras, PySpark, Power BI, Python, SQL, R, Hypothesis Testing</t>
+          <t>RAG, Copilot, CI/CD, Git, Kafka, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb9d13f0cc9eea7</t>
+          <t>https://www.indeed.com/viewjob?jk=db61773e4d860552</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Kafka, Cassandra, R, Optimization</t>
+          <t>Generative AI, RAG, Prompt Engineering, S3, EC2, FastAPI, Docker, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,42 +1511,42 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3887d74faedf394</t>
+          <t>https://www.indeed.com/viewjob?jk=79bf343a6b4ceb21</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer Intern - Generalist</t>
+          <t>Senior Modernization Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Arlo Technologies</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5c5b4ad1fbf2e6</t>
+          <t>https://www.indeed.com/viewjob?jk=405b319cc1a3d05e</t>
         </is>
       </c>
     </row>
@@ -1558,20 +1558,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Copilot, AKS, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d00076775d07a5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Internal Systems Engineer (Applied AI)</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, CI/CD, Git, Python, R, Java</t>
+          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Hadoop, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f1016f224e6b37</t>
+          <t>https://www.indeed.com/viewjob?jk=011e7d4579101ba1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Internal Systems Engineer (Applied AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, CI/CD, Git, Python, R, Java</t>
+          <t>S3, Glue, Redshift, Data Lake, Redshift, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,77 +1651,462 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225a243358c68f49</t>
+          <t>https://www.indeed.com/viewjob?jk=e523bf5a5bf5d62b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Automation Test Architect - Agentic AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, BigQuery, Terraform, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50866ef8a2d7d819</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Decision Scientist III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Terraform, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI Agent Developer – Microsoft Copilot, OpenAI</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Valtech Group</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16d7c867c282b08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Discount Tire</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Specialist - Architecture</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, PySpark, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0a72f863d410844</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AI Enabled Software Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Customer Value Partners (CVP)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5ca3f9ef8402615</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Pinecone, Docker, Kubernetes, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c1b5c7a61c49a06</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Engineer I- Software Edge AI</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Microchip Technology</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
         <v>10</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Snowflake, Tableau, Power BI, MicroStrategy, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Keras, CI/CD, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebd6bd0647e7d139</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AI Developer | Solutioning &amp; Architecture | On site (USA-Based Opportunities)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LogicRays Technologies</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Iselin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, FastAPI, Docker, Kubernetes, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74229b5e609a8c7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Decision Intelligence Engineer - Next Best Action</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, MLflow, Databricks, PySpark, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f925fb9d6621279</t>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b152f84f5f019abe</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Storable</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b13975b57f3203e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Equity Intern</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Bessemer Trust</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7552375a728443df</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Circadence</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tupelo, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59205553c259b012</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-27.xlsx
+++ b/daily_matches/job_matches_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,70 +468,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, LightGBM, S3, Glue, Athena, Kinesis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a9bc2ed7d9f35a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, XGBoost, AWS SageMaker, Azure ML, MLflow, CI/CD, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
+          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
         </is>
       </c>
     </row>
@@ -543,82 +543,82 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
+          <t>RAG, Copilot, S3, Glue, Athena, Docker, Kubernetes, CI/CD, Git, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
+          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, EC2, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>RAG, Copilot, S3, Glue, Athena, Docker, Kubernetes, CI/CD, Git, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4df4e36af097a7</t>
+          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Redshift, Git, Databricks, Redshift, PySpark, Hadoop, Python</t>
+          <t>RAG, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87f70fa8d4be0571</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff097337c23c8bf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, TensorFlow, PyTorch, XGBoost, Glue, PySpark, Tableau, Matplotlib</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1ab8ff9cf591e7</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack Application Developer</t>
+          <t>Research Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Specialty Building Products</t>
+          <t>University of Kansas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Lawrence, KS, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Git, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6435e356286a621f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0b414d2a1faeb6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Distinguished Engineer, AI Applications</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Elevate Digital</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Kubernetes, CI/CD, Snowflake, Kafka</t>
+          <t>AI Engineer, RAG, Prompt Engineering, AKS, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad2682317f293117</t>
+          <t>https://www.indeed.com/viewjob?jk=929c59b599d276dd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Distinguished Engineer, AI Applications</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Kubernetes, CI/CD, Snowflake, Kafka</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b23e7662e6387489</t>
+          <t>https://www.indeed.com/viewjob?jk=f31a5af9350429b9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Distinguished Engineer, AI Applications</t>
+          <t>Senior AWS Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Kubernetes, CI/CD, Snowflake, Kafka</t>
+          <t>S3, Glue, Data Lake, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62b0b0da2ee68ce</t>
+          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Tableau</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
+          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e71383b94e86fbaa</t>
+          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Holtzbrinck Publishing Group</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, Snowflake, BigQuery, PostgreSQL</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6553fe8d88b5cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BigQuery, Kubernetes, CI/CD, Jenkins, Terraform, Git, Snowflake, BigQuery, MySQL, Python</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BigQuery, Kubernetes, CI/CD, Jenkins, Terraform, Git, Snowflake, BigQuery, MySQL, Python</t>
+          <t>Generative AI, Prompt Engineering, CI/CD, Snowflake, Databricks, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Forward Deployed</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Lastwall</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda2c2b8bdd5703d</t>
+          <t>https://www.indeed.com/viewjob?jk=0828ecb52ffde539</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect, GenAI Agentic Networks - Telco</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Mistral, PyTorch, Docker, Kubernetes, NoSQL, Python</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6910545a799b3e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=79aa7fdabf1e2a53</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Junior AI Platform Engineer, Infrastrucure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Glue, Athena, Data Lake, Docker, Terraform, Databricks, NoSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
+          <t>https://www.indeed.com/viewjob?jk=5496a0bc2b4bd3eb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Enabled Software Engineer</t>
+          <t>Senior AI Platform Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Customer Value Partners (CVP)</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b489b3e5c3db2a7</t>
+          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Lyra Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cortex, CI/CD, GitHub Actions, Git, Snowflake, Tableau, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Apache Airflow, Terraform, Snowflake, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Engineer – Microsoft Fabric &amp; Azure AI Foundry</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Valtech Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Power BI, Python</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61ca3c21cedbb70b</t>
+          <t>https://www.indeed.com/viewjob?jk=bab88d8dd775f0fb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Advanced Solution Development Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>KPI Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Glue, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka, SQL</t>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=a56ca99bfe35d05d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer - Fundamental Equities</t>
+          <t>Advanced Solution Development Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>schonfeld</t>
+          <t>KPI Solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, EC2, FastAPI, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, Python</t>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3273ba88ae98348c</t>
+          <t>https://www.indeed.com/viewjob?jk=397dd396f74190be</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Backend Platform Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ClearlyRated</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BigQuery, Dataflow, Kubernetes, CI/CD, Snowflake, BigQuery, Kafka, PostgreSQL, MySQL, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,102 +1336,102 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fe81f0b261447fa</t>
+          <t>https://www.indeed.com/viewjob?jk=010c395bdcd7a30d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Enabled Software Engineer</t>
+          <t>Freelance Solutions Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Customer Value Partners (CVP)</t>
+          <t>Apply</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>S3, EC2, Redshift, Git, Redshift, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33dfe4ea6a65c4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b78398da464c60af</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Kinesis, CI/CD, Terraform, Git, Snowflake, Redshift, Kafka</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
+          <t>https://www.indeed.com/viewjob?jk=46b7b25440101dcc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Engineer - Advisor Software</t>
+          <t>Full-Stack Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Wilson &amp; Company, Inc., Engineers &amp; Architects</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Java, Scala</t>
+          <t>RAG, CI/CD, Git, MySQL, MongoDB, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4621e3a1c0e29479</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16b64e2b8e52d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MES Architect</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>United States Steel</t>
+          <t>Sidecar Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Kafka, MongoDB, Python, SQL, R, Java</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db61773e4d860552</t>
+          <t>https://www.indeed.com/viewjob?jk=c04287fd893caf0c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Sidecar Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, S3, EC2, FastAPI, Docker, CI/CD, Git, Python</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79bf343a6b4ceb21</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f596ccf65df16e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Modernization Architect</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, Kafka, Python, SQL, R, Java</t>
+          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,567 +1546,77 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=405b319cc1a3d05e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
+          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Hadoop, Python, SQL, R, Scala</t>
+          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011e7d4579101ba1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>S3, Glue, Redshift, Data Lake, Redshift, Hadoop, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e523bf5a5bf5d62b</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>BRUNT Workwear</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Terraform, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>BRUNT Workwear</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>North Reading, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Terraform, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>AI Agent Developer – Microsoft Copilot, OpenAI</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Valtech Group</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d7c867c282b08a</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Discount Tire</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Specialist - Architecture</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, PySpark, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0a72f863d410844</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>AI Enabled Software Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Customer Value Partners (CVP)</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ca3f9ef8402615</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Pinecone, Docker, Kubernetes, Git, Kafka, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1b5c7a61c49a06</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Engineer I- Software Edge AI</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Microchip Technology</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Chandler, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, Keras, CI/CD, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd6bd0647e7d139</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>AI Developer | Solutioning &amp; Architecture | On site (USA-Based Opportunities)</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>LogicRays Technologies</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Iselin, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, FastAPI, Docker, Kubernetes, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74229b5e609a8c7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Decision Intelligence Engineer - Next Best Action</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, MLflow, Databricks, PySpark, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b152f84f5f019abe</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Storable</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b13975b57f3203e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Equity Intern</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Bessemer Trust</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7552375a728443df</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Circadence</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Tupelo, MS, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59205553c259b012</t>
+          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-27.xlsx
+++ b/daily_matches/job_matches_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Data Specialist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, LightGBM, S3, Glue, Athena, Kinesis</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Hugging Face, Pinecone, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a9bc2ed7d9f35a</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ddb8e746b2d111</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Radar</t>
+          <t>Green Cabbage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Warrendale, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, XGBoost, AWS SageMaker, Azure ML, MLflow, CI/CD, Git, Kafka</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Keras, NLTK, CI/CD, Git, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
+          <t>https://www.indeed.com/viewjob?jk=f02c103c24d05514</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Athena, Docker, Kubernetes, CI/CD, Git, PySpark</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
+          <t>https://www.indeed.com/viewjob?jk=e99d4b3fc1e7633c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Athena, Docker, Kubernetes, CI/CD, Git, PySpark</t>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
+          <t>https://www.indeed.com/viewjob?jk=affa4e6360039969</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Data Science AI Engineer, Advisor</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Hadoop, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff097337c23c8bf</t>
+          <t>https://www.indeed.com/viewjob?jk=b19c6b7ce515e11c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Terraform, Snowflake, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
+          <t>https://www.indeed.com/viewjob?jk=2655650a85cb9fcd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Research Engineer</t>
+          <t>Software Engineer, Cortex AI Infrastructure</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>University of Kansas</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lawrence, KS, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Git, MySQL, Python, SQL</t>
+          <t>RAG, Cortex, TensorFlow, PyTorch, XGBoost, Kubernetes, CI/CD, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0b414d2a1faeb6</t>
+          <t>https://www.indeed.com/viewjob?jk=7c570bae93be83b6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>AI ML Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Elevate Digital</t>
+          <t>LMK Infotech</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, AKS, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929c59b599d276dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f58281b45bd2f825</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Sr. Software Engineer II - StreamingTV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, BigQuery, FastAPI, Docker, Kubernetes, CI/CD, Snowflake, BigQuery, Kafka, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31a5af9350429b9</t>
+          <t>https://www.indeed.com/viewjob?jk=191cb63cfde4fbba</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer</t>
+          <t>Senior Data Engineer - Product</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, Glue, Data Lake, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, S3, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d76a9122ce202148</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer, Generative AI Systems</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
+          <t>https://www.indeed.com/viewjob?jk=9362dcc4dd475ea0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Terraform, Snowflake, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e069ef7a7b20f315</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Software Engineer II - StreamingTV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>BigQuery, FastAPI, Docker, Kubernetes, CI/CD, Snowflake, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
+          <t>https://www.indeed.com/viewjob?jk=1cd37fa4b89406fc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, CI/CD, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3943ff53d06c45d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Soho Dragon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>Gemini, Copilot, TensorFlow, PyTorch, Keras, OpenCV, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a2ae1bbe9c3634</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Engineering</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, CI/CD, Snowflake, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, Git, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ba2691830b117c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Product Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lastwall</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
+          <t>RAG, S3, Docker, Kubernetes, PostgreSQL, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0828ecb52ffde539</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Radar</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Hugging Face, PyTorch, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79aa7fdabf1e2a53</t>
+          <t>https://www.indeed.com/viewjob?jk=11098d0fb738bb19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Junior AI Platform Engineer, Infrastrucure</t>
+          <t>AI &amp; Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Lightspeed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5496a0bc2b4bd3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=77a681f899ba3da6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer, Infrastructure</t>
+          <t>Software Engineer GenAI - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, MySQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
+          <t>https://www.indeed.com/viewjob?jk=38488e180644fae6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Analyst V (6183)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lyra Health</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Apache Airflow, Terraform, Snowflake, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
+          <t>https://www.indeed.com/viewjob?jk=e40e6d647e978f6f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Sr Analyst, AI Transformation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab88d8dd775f0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=12f4772489611d58</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Advanced Solution Development Data Scientist</t>
+          <t>Java Software Engineer, Intermediate</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KPI Solutions</t>
+          <t>Ingram Content Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>La Vergne, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, AKS, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56ca99bfe35d05d</t>
+          <t>https://www.indeed.com/viewjob?jk=b5332e786f98b3db</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Advanced Solution Development Data Scientist</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KPI Solutions</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>Copilot, Jenkins, Git, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=397dd396f74190be</t>
+          <t>https://www.indeed.com/viewjob?jk=351ed2ddd56d5d3d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c395bdcd7a30d</t>
+          <t>https://www.indeed.com/viewjob?jk=f54a2d70472a06f4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Freelance Solutions Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Apply</t>
+          <t>Celigo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>S3, EC2, Redshift, Git, Redshift, SQL, R, Java, Scala</t>
+          <t>BigQuery, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78398da464c60af</t>
+          <t>https://www.indeed.com/viewjob?jk=5b4364b98aa491d2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Partner Solutions Engineer - Red Hat Platforms</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Git, PostgreSQL, SQL, R</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,217 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b7b25440101dcc</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Full-Stack Developer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Wilson &amp; Company, Inc., Engineers &amp; Architects</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, MySQL, MongoDB, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16b64e2b8e52d</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Sidecar Health</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c04287fd893caf0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Sidecar Health</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f596ccf65df16e</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Data Solution Architect</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Baker Tilly Canada</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Data Solution Architect</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Baker Tilly Canada</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Data Solution Architect</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Baker Tilly Canada</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Madison, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3837d2847f0d7c</t>
         </is>
       </c>
     </row>
